--- a/public/data/pricing_standard.xlsx
+++ b/public/data/pricing_standard.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N21"/>
+  <dimension ref="A1:N39"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -445,13 +445,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>34a4a596-1609-4391-82fa-347a061c784c</v>
+        <v>b14da057-d399-4899-be81-4d33dd8ac607</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C2" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D2" t="str">
         <v>CTR-001-001</v>
@@ -460,10 +460,10 @@
         <v>["Mon","Tue","Wed","Thu","Fri","Sat","Sun"]</v>
       </c>
       <c r="F2" t="str">
-        <v>53bca1fc-519c-458e-91f3-f73ab9c834fe</v>
+        <v>ebf035b5-c1d1-4e4e-b99a-0fa6b0fcbdb0</v>
       </c>
       <c r="G2" t="str">
-        <v>53bca1fc-519c-458e-91f3-f73ab9c834fe</v>
+        <v>ebf035b5-c1d1-4e4e-b99a-0fa6b0fcbdb0</v>
       </c>
       <c r="H2" t="str">
         <v>Seaplane</v>
@@ -484,18 +484,18 @@
         <v>2025-01-01</v>
       </c>
       <c r="N2" t="str">
-        <v>2025-12-31</v>
+        <v>2026-03-01</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>111dc08d-b1f9-4e13-92e2-5c05cbc9607b</v>
+        <v>28b3c775-48cd-4918-a969-04c08f686eca</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C3" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D3" t="str">
         <v>CTR-001-001</v>
@@ -504,10 +504,10 @@
         <v>["Mon","Tue","Wed","Thu","Fri","Sat","Sun"]</v>
       </c>
       <c r="F3" t="str">
-        <v>53bca1fc-519c-458e-91f3-f73ab9c834fe</v>
+        <v>ebf035b5-c1d1-4e4e-b99a-0fa6b0fcbdb0</v>
       </c>
       <c r="G3" t="str">
-        <v>53bca1fc-519c-458e-91f3-f73ab9c834fe</v>
+        <v>ebf035b5-c1d1-4e4e-b99a-0fa6b0fcbdb0</v>
       </c>
       <c r="H3" t="str">
         <v>Seaplane</v>
@@ -528,30 +528,30 @@
         <v>2025-01-01</v>
       </c>
       <c r="N3" t="str">
-        <v>2025-12-31</v>
+        <v>2026-03-01</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>49f9e1b0-0dc1-4c01-830d-e95eb4dde4ee</v>
+        <v>9ed1d6a6-998a-4229-9e78-a82fd61c88b3</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C4" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D4" t="str">
-        <v>CTR-002-001</v>
+        <v>CTR-001-002</v>
       </c>
       <c r="E4" t="str">
         <v>["Mon","Tue","Wed","Thu","Fri","Sat","Sun"]</v>
       </c>
       <c r="F4" t="str">
-        <v>819129ff-9f49-45d0-92b3-d595220fdfb5</v>
+        <v>ebf035b5-c1d1-4e4e-b99a-0fa6b0fcbdb0</v>
       </c>
       <c r="G4" t="str">
-        <v>819129ff-9f49-45d0-92b3-d595220fdfb5</v>
+        <v>ebf035b5-c1d1-4e4e-b99a-0fa6b0fcbdb0</v>
       </c>
       <c r="H4" t="str">
         <v>Seaplane</v>
@@ -563,39 +563,39 @@
         <v>Adult</v>
       </c>
       <c r="K4">
-        <v>620</v>
+        <v>850</v>
       </c>
       <c r="L4">
-        <v>370</v>
+        <v>500</v>
       </c>
       <c r="M4" t="str">
-        <v>2025-03-01</v>
+        <v>2025-06-01</v>
       </c>
       <c r="N4" t="str">
-        <v>2026-02-28</v>
+        <v>2026-05-31</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>73630be0-e085-48fd-b1cb-f687ec213381</v>
+        <v>380b1d13-4b52-4dcb-832f-80002d0c81e2</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C5" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D5" t="str">
-        <v>CTR-002-001</v>
+        <v>CTR-001-002</v>
       </c>
       <c r="E5" t="str">
         <v>["Mon","Tue","Wed","Thu","Fri","Sat","Sun"]</v>
       </c>
       <c r="F5" t="str">
-        <v>819129ff-9f49-45d0-92b3-d595220fdfb5</v>
+        <v>ebf035b5-c1d1-4e4e-b99a-0fa6b0fcbdb0</v>
       </c>
       <c r="G5" t="str">
-        <v>819129ff-9f49-45d0-92b3-d595220fdfb5</v>
+        <v>ebf035b5-c1d1-4e4e-b99a-0fa6b0fcbdb0</v>
       </c>
       <c r="H5" t="str">
         <v>Seaplane</v>
@@ -607,39 +607,39 @@
         <v>Child</v>
       </c>
       <c r="K5">
-        <v>370</v>
+        <v>510</v>
       </c>
       <c r="L5">
-        <v>220</v>
+        <v>300</v>
       </c>
       <c r="M5" t="str">
-        <v>2025-03-01</v>
+        <v>2025-06-01</v>
       </c>
       <c r="N5" t="str">
-        <v>2026-02-28</v>
+        <v>2026-05-31</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>3796810c-c6c0-46ea-98ba-48b2ae32ed8b</v>
+        <v>f6221ca4-a31e-4d8a-9649-0175d08ad66e</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C6" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D6" t="str">
-        <v>CTR-003-001</v>
+        <v>CTR-002-001</v>
       </c>
       <c r="E6" t="str">
         <v>["Mon","Tue","Wed","Thu","Fri","Sat","Sun"]</v>
       </c>
       <c r="F6" t="str">
-        <v>99492203-f941-48e8-923d-076e492f5230</v>
+        <v>42e6bcee-426a-4f7a-877e-20c9962142d5</v>
       </c>
       <c r="G6" t="str">
-        <v>99492203-f941-48e8-923d-076e492f5230</v>
+        <v>42e6bcee-426a-4f7a-877e-20c9962142d5</v>
       </c>
       <c r="H6" t="str">
         <v>Seaplane</v>
@@ -651,39 +651,39 @@
         <v>Adult</v>
       </c>
       <c r="K6">
-        <v>600</v>
+        <v>620</v>
       </c>
       <c r="L6">
-        <v>350</v>
+        <v>370</v>
       </c>
       <c r="M6" t="str">
-        <v>2025-06-01</v>
+        <v>2025-03-01</v>
       </c>
       <c r="N6" t="str">
-        <v>2026-05-31</v>
+        <v>2027-02-28</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>f60e0086-2f6a-4c74-8870-679ae8037edb</v>
+        <v>3bfbc8a4-62b3-4bce-bb74-068e6dd44e4c</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C7" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D7" t="str">
-        <v>CTR-003-001</v>
+        <v>CTR-002-001</v>
       </c>
       <c r="E7" t="str">
         <v>["Mon","Tue","Wed","Thu","Fri","Sat","Sun"]</v>
       </c>
       <c r="F7" t="str">
-        <v>99492203-f941-48e8-923d-076e492f5230</v>
+        <v>42e6bcee-426a-4f7a-877e-20c9962142d5</v>
       </c>
       <c r="G7" t="str">
-        <v>99492203-f941-48e8-923d-076e492f5230</v>
+        <v>42e6bcee-426a-4f7a-877e-20c9962142d5</v>
       </c>
       <c r="H7" t="str">
         <v>Seaplane</v>
@@ -695,39 +695,39 @@
         <v>Child</v>
       </c>
       <c r="K7">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="L7">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="M7" t="str">
-        <v>2025-06-01</v>
+        <v>2025-03-01</v>
       </c>
       <c r="N7" t="str">
-        <v>2026-05-31</v>
+        <v>2027-02-28</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>84cdfbf9-4d68-445c-a214-8466691b8211</v>
+        <v>ffa7bddc-5c19-42f6-b7d0-f6616785e41f</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C8" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D8" t="str">
-        <v>CTR-004-001</v>
+        <v>CTR-003-001</v>
       </c>
       <c r="E8" t="str">
         <v>["Mon","Tue","Wed","Thu","Fri","Sat","Sun"]</v>
       </c>
       <c r="F8" t="str">
-        <v>ae61d497-ed25-4ed3-b6f5-07f017123cbd</v>
+        <v>8c495640-1ad6-4fe8-a0e6-d51bbcc503c9</v>
       </c>
       <c r="G8" t="str">
-        <v>ae61d497-ed25-4ed3-b6f5-07f017123cbd</v>
+        <v>8c495640-1ad6-4fe8-a0e6-d51bbcc503c9</v>
       </c>
       <c r="H8" t="str">
         <v>Seaplane</v>
@@ -739,39 +739,39 @@
         <v>Adult</v>
       </c>
       <c r="K8">
-        <v>740</v>
+        <v>750</v>
       </c>
       <c r="L8">
         <v>440</v>
       </c>
       <c r="M8" t="str">
-        <v>2024-01-01</v>
+        <v>2025-06-01</v>
       </c>
       <c r="N8" t="str">
-        <v>2024-12-31</v>
+        <v>2027-05-31</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>f6f9a4a3-c2ca-4d5f-a961-c8e1696c28d2</v>
+        <v>b45e1a53-6096-4113-ab42-3ab481f95dcd</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C9" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D9" t="str">
-        <v>CTR-004-001</v>
+        <v>CTR-003-001</v>
       </c>
       <c r="E9" t="str">
         <v>["Mon","Tue","Wed","Thu","Fri","Sat","Sun"]</v>
       </c>
       <c r="F9" t="str">
-        <v>ae61d497-ed25-4ed3-b6f5-07f017123cbd</v>
+        <v>8c495640-1ad6-4fe8-a0e6-d51bbcc503c9</v>
       </c>
       <c r="G9" t="str">
-        <v>ae61d497-ed25-4ed3-b6f5-07f017123cbd</v>
+        <v>8c495640-1ad6-4fe8-a0e6-d51bbcc503c9</v>
       </c>
       <c r="H9" t="str">
         <v>Seaplane</v>
@@ -783,39 +783,39 @@
         <v>Child</v>
       </c>
       <c r="K9">
-        <v>440</v>
+        <v>450</v>
       </c>
       <c r="L9">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="M9" t="str">
-        <v>2024-01-01</v>
+        <v>2025-06-01</v>
       </c>
       <c r="N9" t="str">
-        <v>2024-12-31</v>
+        <v>2027-05-31</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>e5f8612d-cae8-42f6-8003-bce6087e56cb</v>
+        <v>c1998332-6652-4bb8-af08-705527f34209</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C10" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D10" t="str">
-        <v>CTR-005-001</v>
+        <v>CTR-003-002</v>
       </c>
       <c r="E10" t="str">
         <v>["Mon","Tue","Wed","Thu","Fri","Sat","Sun"]</v>
       </c>
       <c r="F10" t="str">
-        <v>44e8275f-6dbf-4a68-8aa8-3a6a09ecac5e</v>
+        <v>8c495640-1ad6-4fe8-a0e6-d51bbcc503c9</v>
       </c>
       <c r="G10" t="str">
-        <v>44e8275f-6dbf-4a68-8aa8-3a6a09ecac5e</v>
+        <v>8c495640-1ad6-4fe8-a0e6-d51bbcc503c9</v>
       </c>
       <c r="H10" t="str">
         <v>Seaplane</v>
@@ -827,39 +827,39 @@
         <v>Adult</v>
       </c>
       <c r="K10">
-        <v>590</v>
+        <v>600</v>
       </c>
       <c r="L10">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="M10" t="str">
-        <v>2025-04-01</v>
+        <v>2025-06-01</v>
       </c>
       <c r="N10" t="str">
-        <v>2026-03-31</v>
+        <v>2026-12-31</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>4b57bfee-c8ba-4f79-bf88-ab64a05696c0</v>
+        <v>f2bac5d1-3cc4-42d5-8eec-1c98d7de11c7</v>
       </c>
       <c r="B11" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C11" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D11" t="str">
-        <v>CTR-005-001</v>
+        <v>CTR-003-002</v>
       </c>
       <c r="E11" t="str">
         <v>["Mon","Tue","Wed","Thu","Fri","Sat","Sun"]</v>
       </c>
       <c r="F11" t="str">
-        <v>44e8275f-6dbf-4a68-8aa8-3a6a09ecac5e</v>
+        <v>8c495640-1ad6-4fe8-a0e6-d51bbcc503c9</v>
       </c>
       <c r="G11" t="str">
-        <v>44e8275f-6dbf-4a68-8aa8-3a6a09ecac5e</v>
+        <v>8c495640-1ad6-4fe8-a0e6-d51bbcc503c9</v>
       </c>
       <c r="H11" t="str">
         <v>Seaplane</v>
@@ -871,39 +871,39 @@
         <v>Child</v>
       </c>
       <c r="K11">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="L11">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="M11" t="str">
-        <v>2025-04-01</v>
+        <v>2025-06-01</v>
       </c>
       <c r="N11" t="str">
-        <v>2026-03-31</v>
+        <v>2026-12-31</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ef920359-6ab5-46a9-9a39-417637f5ba22</v>
+        <v>86d50382-dd25-4626-8914-2d933aa5e033</v>
       </c>
       <c r="B12" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C12" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D12" t="str">
-        <v>CTR-006-001</v>
+        <v>CTR-003-003</v>
       </c>
       <c r="E12" t="str">
         <v>["Mon","Tue","Wed","Thu","Fri","Sat","Sun"]</v>
       </c>
       <c r="F12" t="str">
-        <v>c4b72dfb-694a-4cd6-a5be-cb1bddcaa2a5</v>
+        <v>8c495640-1ad6-4fe8-a0e6-d51bbcc503c9</v>
       </c>
       <c r="G12" t="str">
-        <v>c4b72dfb-694a-4cd6-a5be-cb1bddcaa2a5</v>
+        <v>8c495640-1ad6-4fe8-a0e6-d51bbcc503c9</v>
       </c>
       <c r="H12" t="str">
         <v>Seaplane</v>
@@ -915,39 +915,39 @@
         <v>Adult</v>
       </c>
       <c r="K12">
-        <v>640</v>
+        <v>900</v>
       </c>
       <c r="L12">
-        <v>380</v>
+        <v>530</v>
       </c>
       <c r="M12" t="str">
-        <v>2026-01-01</v>
+        <v>2025-10-01</v>
       </c>
       <c r="N12" t="str">
-        <v>2026-12-31</v>
+        <v>2026-09-30</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>a896e3c3-5c5c-4538-a9c7-a874eae4849c</v>
+        <v>d3ee1b0b-a0ac-4b02-a846-ba2dc54de08d</v>
       </c>
       <c r="B13" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C13" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D13" t="str">
-        <v>CTR-006-001</v>
+        <v>CTR-003-003</v>
       </c>
       <c r="E13" t="str">
         <v>["Mon","Tue","Wed","Thu","Fri","Sat","Sun"]</v>
       </c>
       <c r="F13" t="str">
-        <v>c4b72dfb-694a-4cd6-a5be-cb1bddcaa2a5</v>
+        <v>8c495640-1ad6-4fe8-a0e6-d51bbcc503c9</v>
       </c>
       <c r="G13" t="str">
-        <v>c4b72dfb-694a-4cd6-a5be-cb1bddcaa2a5</v>
+        <v>8c495640-1ad6-4fe8-a0e6-d51bbcc503c9</v>
       </c>
       <c r="H13" t="str">
         <v>Seaplane</v>
@@ -959,42 +959,42 @@
         <v>Child</v>
       </c>
       <c r="K13">
-        <v>385</v>
+        <v>540</v>
       </c>
       <c r="L13">
-        <v>228</v>
+        <v>318</v>
       </c>
       <c r="M13" t="str">
-        <v>2026-01-01</v>
+        <v>2025-10-01</v>
       </c>
       <c r="N13" t="str">
-        <v>2026-12-31</v>
+        <v>2026-09-30</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>973db92a-0a36-4465-8787-b4cffc41321b</v>
+        <v>3b15c6b6-06c3-4449-8a12-beb871b6bc0b</v>
       </c>
       <c r="B14" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C14" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D14" t="str">
-        <v>CTR-007-001</v>
+        <v>CTR-004-001</v>
       </c>
       <c r="E14" t="str">
         <v>["Mon","Tue","Wed","Thu","Fri","Sat","Sun"]</v>
       </c>
       <c r="F14" t="str">
-        <v>9fda538c-f70f-447b-9d9a-f641700abf98</v>
+        <v>c4b758b0-8279-41c1-9617-c33355bf329a</v>
       </c>
       <c r="G14" t="str">
-        <v>9fda538c-f70f-447b-9d9a-f641700abf98</v>
+        <v>c4b758b0-8279-41c1-9617-c33355bf329a</v>
       </c>
       <c r="H14" t="str">
-        <v>Speedboat</v>
+        <v>Seaplane</v>
       </c>
       <c r="I14" t="str">
         <v/>
@@ -1003,42 +1003,42 @@
         <v>Adult</v>
       </c>
       <c r="K14">
-        <v>320</v>
+        <v>740</v>
       </c>
       <c r="L14">
-        <v>190</v>
+        <v>440</v>
       </c>
       <c r="M14" t="str">
-        <v>2025-01-01</v>
+        <v>2024-01-01</v>
       </c>
       <c r="N14" t="str">
-        <v>2026-03-10</v>
+        <v>2024-12-31</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>549012a5-601e-4afe-a24f-0c0401604b85</v>
+        <v>4bb4d804-c953-42dc-98cb-1b4431a7f5d7</v>
       </c>
       <c r="B15" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C15" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D15" t="str">
-        <v>CTR-007-001</v>
+        <v>CTR-004-001</v>
       </c>
       <c r="E15" t="str">
         <v>["Mon","Tue","Wed","Thu","Fri","Sat","Sun"]</v>
       </c>
       <c r="F15" t="str">
-        <v>9fda538c-f70f-447b-9d9a-f641700abf98</v>
+        <v>c4b758b0-8279-41c1-9617-c33355bf329a</v>
       </c>
       <c r="G15" t="str">
-        <v>9fda538c-f70f-447b-9d9a-f641700abf98</v>
+        <v>c4b758b0-8279-41c1-9617-c33355bf329a</v>
       </c>
       <c r="H15" t="str">
-        <v>Speedboat</v>
+        <v>Seaplane</v>
       </c>
       <c r="I15" t="str">
         <v>Age 2-11</v>
@@ -1047,39 +1047,39 @@
         <v>Child</v>
       </c>
       <c r="K15">
-        <v>190</v>
+        <v>440</v>
       </c>
       <c r="L15">
-        <v>115</v>
+        <v>260</v>
       </c>
       <c r="M15" t="str">
-        <v>2025-01-01</v>
+        <v>2024-01-01</v>
       </c>
       <c r="N15" t="str">
-        <v>2026-03-10</v>
+        <v>2024-12-31</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>e9bead4a-ac5d-4ab6-95a0-20b419bd6fe4</v>
+        <v>afc7be75-aa6a-407c-ba83-5bed3009c8a3</v>
       </c>
       <c r="B16" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C16" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D16" t="str">
-        <v>CTR-008-001</v>
+        <v>CTR-005-001</v>
       </c>
       <c r="E16" t="str">
         <v>["Mon","Tue","Wed","Thu","Fri","Sat","Sun"]</v>
       </c>
       <c r="F16" t="str">
-        <v>79958ed2-9c5b-421b-98f3-26062254d840</v>
+        <v>bc4b67a6-ea9d-4639-ba7b-e1c4adfbc48c</v>
       </c>
       <c r="G16" t="str">
-        <v>79958ed2-9c5b-421b-98f3-26062254d840</v>
+        <v>bc4b67a6-ea9d-4639-ba7b-e1c4adfbc48c</v>
       </c>
       <c r="H16" t="str">
         <v>Seaplane</v>
@@ -1091,39 +1091,39 @@
         <v>Adult</v>
       </c>
       <c r="K16">
-        <v>660</v>
+        <v>590</v>
       </c>
       <c r="L16">
-        <v>390</v>
+        <v>345</v>
       </c>
       <c r="M16" t="str">
-        <v>2025-10-01</v>
+        <v>2025-04-01</v>
       </c>
       <c r="N16" t="str">
-        <v>2026-09-30</v>
+        <v>2027-03-31</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>a04c06d6-ee75-4a4c-a64c-f385ad9d58e1</v>
+        <v>db7410da-9808-42b9-944f-e3428493da05</v>
       </c>
       <c r="B17" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C17" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D17" t="str">
-        <v>CTR-008-001</v>
+        <v>CTR-005-001</v>
       </c>
       <c r="E17" t="str">
         <v>["Mon","Tue","Wed","Thu","Fri","Sat","Sun"]</v>
       </c>
       <c r="F17" t="str">
-        <v>79958ed2-9c5b-421b-98f3-26062254d840</v>
+        <v>bc4b67a6-ea9d-4639-ba7b-e1c4adfbc48c</v>
       </c>
       <c r="G17" t="str">
-        <v>79958ed2-9c5b-421b-98f3-26062254d840</v>
+        <v>bc4b67a6-ea9d-4639-ba7b-e1c4adfbc48c</v>
       </c>
       <c r="H17" t="str">
         <v>Seaplane</v>
@@ -1135,42 +1135,42 @@
         <v>Child</v>
       </c>
       <c r="K17">
-        <v>395</v>
+        <v>355</v>
       </c>
       <c r="L17">
-        <v>234</v>
+        <v>207</v>
       </c>
       <c r="M17" t="str">
-        <v>2025-10-01</v>
+        <v>2025-04-01</v>
       </c>
       <c r="N17" t="str">
-        <v>2026-09-30</v>
+        <v>2027-03-31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>84075cfb-f45a-4f44-bcb9-5e21d18f5504</v>
+        <v>40d1aadf-8cff-47e3-97a4-9e0652422f2a</v>
       </c>
       <c r="B18" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C18" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D18" t="str">
-        <v>CTR-009-001</v>
+        <v>CTR-005-002</v>
       </c>
       <c r="E18" t="str">
         <v>["Mon","Tue","Wed","Thu","Fri","Sat","Sun"]</v>
       </c>
       <c r="F18" t="str">
-        <v>28f29363-bd63-4176-95b1-4de2fd79edf4</v>
+        <v>bc4b67a6-ea9d-4639-ba7b-e1c4adfbc48c</v>
       </c>
       <c r="G18" t="str">
-        <v>28f29363-bd63-4176-95b1-4de2fd79edf4</v>
+        <v>bc4b67a6-ea9d-4639-ba7b-e1c4adfbc48c</v>
       </c>
       <c r="H18" t="str">
-        <v>Speedboat</v>
+        <v>Seaplane</v>
       </c>
       <c r="I18" t="str">
         <v/>
@@ -1179,10 +1179,10 @@
         <v>Adult</v>
       </c>
       <c r="K18">
-        <v>350</v>
+        <v>780</v>
       </c>
       <c r="L18">
-        <v>210</v>
+        <v>460</v>
       </c>
       <c r="M18" t="str">
         <v>2025-11-01</v>
@@ -1193,28 +1193,28 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>4ca02de4-be62-4d50-b875-6aed0f8bc99a</v>
+        <v>e847d8ef-871c-4ae4-8dae-8129a24ba758</v>
       </c>
       <c r="B19" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C19" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D19" t="str">
-        <v>CTR-009-001</v>
+        <v>CTR-005-002</v>
       </c>
       <c r="E19" t="str">
         <v>["Mon","Tue","Wed","Thu","Fri","Sat","Sun"]</v>
       </c>
       <c r="F19" t="str">
-        <v>28f29363-bd63-4176-95b1-4de2fd79edf4</v>
+        <v>bc4b67a6-ea9d-4639-ba7b-e1c4adfbc48c</v>
       </c>
       <c r="G19" t="str">
-        <v>28f29363-bd63-4176-95b1-4de2fd79edf4</v>
+        <v>bc4b67a6-ea9d-4639-ba7b-e1c4adfbc48c</v>
       </c>
       <c r="H19" t="str">
-        <v>Speedboat</v>
+        <v>Seaplane</v>
       </c>
       <c r="I19" t="str">
         <v>Age 2-11</v>
@@ -1223,10 +1223,10 @@
         <v>Child</v>
       </c>
       <c r="K19">
-        <v>210</v>
+        <v>468</v>
       </c>
       <c r="L19">
-        <v>125</v>
+        <v>276</v>
       </c>
       <c r="M19" t="str">
         <v>2025-11-01</v>
@@ -1237,25 +1237,25 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>4a46c806-f3d5-475a-a3bf-184560d450cd</v>
+        <v>f4e61566-b88f-4d58-8269-0f4e866f5d7f</v>
       </c>
       <c r="B20" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C20" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D20" t="str">
-        <v>CTR-010-001</v>
+        <v>CTR-006-001</v>
       </c>
       <c r="E20" t="str">
         <v>["Mon","Tue","Wed","Thu","Fri","Sat","Sun"]</v>
       </c>
       <c r="F20" t="str">
-        <v>b2c6555b-31b8-470c-a25d-e7b05dadb044</v>
+        <v>57aee1f6-06da-4322-8c0f-f0d0d82a1a31</v>
       </c>
       <c r="G20" t="str">
-        <v>b2c6555b-31b8-470c-a25d-e7b05dadb044</v>
+        <v>57aee1f6-06da-4322-8c0f-f0d0d82a1a31</v>
       </c>
       <c r="H20" t="str">
         <v>Seaplane</v>
@@ -1267,39 +1267,39 @@
         <v>Adult</v>
       </c>
       <c r="K20">
-        <v>710</v>
+        <v>640</v>
       </c>
       <c r="L20">
-        <v>420</v>
+        <v>380</v>
       </c>
       <c r="M20" t="str">
-        <v>2024-03-01</v>
+        <v>2025-01-01</v>
       </c>
       <c r="N20" t="str">
-        <v>2025-02-28</v>
+        <v>2027-12-31</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>d306384e-84e4-4291-8fb4-b41521abaa99</v>
+        <v>2b8d2669-f2f8-46e7-a579-9d35d4c8817c</v>
       </c>
       <c r="B21" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C21" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D21" t="str">
-        <v>CTR-010-001</v>
+        <v>CTR-006-001</v>
       </c>
       <c r="E21" t="str">
         <v>["Mon","Tue","Wed","Thu","Fri","Sat","Sun"]</v>
       </c>
       <c r="F21" t="str">
-        <v>b2c6555b-31b8-470c-a25d-e7b05dadb044</v>
+        <v>57aee1f6-06da-4322-8c0f-f0d0d82a1a31</v>
       </c>
       <c r="G21" t="str">
-        <v>b2c6555b-31b8-470c-a25d-e7b05dadb044</v>
+        <v>57aee1f6-06da-4322-8c0f-f0d0d82a1a31</v>
       </c>
       <c r="H21" t="str">
         <v>Seaplane</v>
@@ -1311,21 +1311,813 @@
         <v>Child</v>
       </c>
       <c r="K21">
+        <v>385</v>
+      </c>
+      <c r="L21">
+        <v>228</v>
+      </c>
+      <c r="M21" t="str">
+        <v>2025-01-01</v>
+      </c>
+      <c r="N21" t="str">
+        <v>2027-12-31</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>62d0ec91-c81e-43e9-a888-767a8c0ff75a</v>
+      </c>
+      <c r="B22" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C22" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D22" t="str">
+        <v>CTR-006-002</v>
+      </c>
+      <c r="E22" t="str">
+        <v>["Mon","Tue","Wed","Thu","Fri","Sat","Sun"]</v>
+      </c>
+      <c r="F22" t="str">
+        <v>57aee1f6-06da-4322-8c0f-f0d0d82a1a31</v>
+      </c>
+      <c r="G22" t="str">
+        <v>57aee1f6-06da-4322-8c0f-f0d0d82a1a31</v>
+      </c>
+      <c r="H22" t="str">
+        <v>Seaplane</v>
+      </c>
+      <c r="I22" t="str">
+        <v/>
+      </c>
+      <c r="J22" t="str">
+        <v>Adult</v>
+      </c>
+      <c r="K22">
+        <v>820</v>
+      </c>
+      <c r="L22">
+        <v>485</v>
+      </c>
+      <c r="M22" t="str">
+        <v>2025-06-01</v>
+      </c>
+      <c r="N22" t="str">
+        <v>2027-05-31</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>c3fc00db-7fe1-47d0-a6b2-f0887daddc01</v>
+      </c>
+      <c r="B23" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C23" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D23" t="str">
+        <v>CTR-006-002</v>
+      </c>
+      <c r="E23" t="str">
+        <v>["Mon","Tue","Wed","Thu","Fri","Sat","Sun"]</v>
+      </c>
+      <c r="F23" t="str">
+        <v>57aee1f6-06da-4322-8c0f-f0d0d82a1a31</v>
+      </c>
+      <c r="G23" t="str">
+        <v>57aee1f6-06da-4322-8c0f-f0d0d82a1a31</v>
+      </c>
+      <c r="H23" t="str">
+        <v>Seaplane</v>
+      </c>
+      <c r="I23" t="str">
+        <v>Age 2-11</v>
+      </c>
+      <c r="J23" t="str">
+        <v>Child</v>
+      </c>
+      <c r="K23">
+        <v>492</v>
+      </c>
+      <c r="L23">
+        <v>291</v>
+      </c>
+      <c r="M23" t="str">
+        <v>2025-06-01</v>
+      </c>
+      <c r="N23" t="str">
+        <v>2027-05-31</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>c1cedbd7-b78c-4dbb-81d1-d865723b0da6</v>
+      </c>
+      <c r="B24" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C24" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D24" t="str">
+        <v>CTR-006-003</v>
+      </c>
+      <c r="E24" t="str">
+        <v>["Mon","Tue","Wed","Thu","Fri","Sat","Sun"]</v>
+      </c>
+      <c r="F24" t="str">
+        <v>57aee1f6-06da-4322-8c0f-f0d0d82a1a31</v>
+      </c>
+      <c r="G24" t="str">
+        <v>57aee1f6-06da-4322-8c0f-f0d0d82a1a31</v>
+      </c>
+      <c r="H24" t="str">
+        <v>Seaplane</v>
+      </c>
+      <c r="I24" t="str">
+        <v/>
+      </c>
+      <c r="J24" t="str">
+        <v>Adult</v>
+      </c>
+      <c r="K24">
+        <v>950</v>
+      </c>
+      <c r="L24">
+        <v>560</v>
+      </c>
+      <c r="M24" t="str">
+        <v>2026-01-01</v>
+      </c>
+      <c r="N24" t="str">
+        <v>2026-12-31</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>1d7d4f31-6362-4e97-9e15-5b484e0743b1</v>
+      </c>
+      <c r="B25" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C25" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D25" t="str">
+        <v>CTR-006-003</v>
+      </c>
+      <c r="E25" t="str">
+        <v>["Mon","Tue","Wed","Thu","Fri","Sat","Sun"]</v>
+      </c>
+      <c r="F25" t="str">
+        <v>57aee1f6-06da-4322-8c0f-f0d0d82a1a31</v>
+      </c>
+      <c r="G25" t="str">
+        <v>57aee1f6-06da-4322-8c0f-f0d0d82a1a31</v>
+      </c>
+      <c r="H25" t="str">
+        <v>Seaplane</v>
+      </c>
+      <c r="I25" t="str">
+        <v>Age 2-11</v>
+      </c>
+      <c r="J25" t="str">
+        <v>Child</v>
+      </c>
+      <c r="K25">
+        <v>570</v>
+      </c>
+      <c r="L25">
+        <v>336</v>
+      </c>
+      <c r="M25" t="str">
+        <v>2026-01-01</v>
+      </c>
+      <c r="N25" t="str">
+        <v>2026-12-31</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>4ad253cf-4c59-4d16-a300-8e3e89975f96</v>
+      </c>
+      <c r="B26" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C26" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D26" t="str">
+        <v>CTR-007-001</v>
+      </c>
+      <c r="E26" t="str">
+        <v>["Mon","Tue","Wed","Thu","Fri","Sat","Sun"]</v>
+      </c>
+      <c r="F26" t="str">
+        <v>a6635d78-8321-470b-ba54-19fb00ecc897</v>
+      </c>
+      <c r="G26" t="str">
+        <v>a6635d78-8321-470b-ba54-19fb00ecc897</v>
+      </c>
+      <c r="H26" t="str">
+        <v>Speedboat</v>
+      </c>
+      <c r="I26" t="str">
+        <v/>
+      </c>
+      <c r="J26" t="str">
+        <v>Adult</v>
+      </c>
+      <c r="K26">
+        <v>320</v>
+      </c>
+      <c r="L26">
+        <v>190</v>
+      </c>
+      <c r="M26" t="str">
+        <v>2025-01-01</v>
+      </c>
+      <c r="N26" t="str">
+        <v>2026-03-10</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>90664373-0ec3-4523-9edf-aa9dea7b0069</v>
+      </c>
+      <c r="B27" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C27" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D27" t="str">
+        <v>CTR-007-001</v>
+      </c>
+      <c r="E27" t="str">
+        <v>["Mon","Tue","Wed","Thu","Fri","Sat","Sun"]</v>
+      </c>
+      <c r="F27" t="str">
+        <v>a6635d78-8321-470b-ba54-19fb00ecc897</v>
+      </c>
+      <c r="G27" t="str">
+        <v>a6635d78-8321-470b-ba54-19fb00ecc897</v>
+      </c>
+      <c r="H27" t="str">
+        <v>Speedboat</v>
+      </c>
+      <c r="I27" t="str">
+        <v>Age 2-11</v>
+      </c>
+      <c r="J27" t="str">
+        <v>Child</v>
+      </c>
+      <c r="K27">
+        <v>190</v>
+      </c>
+      <c r="L27">
+        <v>115</v>
+      </c>
+      <c r="M27" t="str">
+        <v>2025-01-01</v>
+      </c>
+      <c r="N27" t="str">
+        <v>2026-03-10</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>631e40e6-447e-4fdf-a766-9dc6d4053f10</v>
+      </c>
+      <c r="B28" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C28" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D28" t="str">
+        <v>CTR-007-002</v>
+      </c>
+      <c r="E28" t="str">
+        <v>["Mon","Tue","Wed","Thu","Fri","Sat","Sun"]</v>
+      </c>
+      <c r="F28" t="str">
+        <v>a6635d78-8321-470b-ba54-19fb00ecc897</v>
+      </c>
+      <c r="G28" t="str">
+        <v>a6635d78-8321-470b-ba54-19fb00ecc897</v>
+      </c>
+      <c r="H28" t="str">
+        <v>Seaplane</v>
+      </c>
+      <c r="I28" t="str">
+        <v/>
+      </c>
+      <c r="J28" t="str">
+        <v>Adult</v>
+      </c>
+      <c r="K28">
+        <v>520</v>
+      </c>
+      <c r="L28">
+        <v>310</v>
+      </c>
+      <c r="M28" t="str">
+        <v>2025-01-01</v>
+      </c>
+      <c r="N28" t="str">
+        <v>2026-03-10</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>26678c5a-d9dc-49ef-b982-0cfba38d0a7e</v>
+      </c>
+      <c r="B29" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C29" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D29" t="str">
+        <v>CTR-007-002</v>
+      </c>
+      <c r="E29" t="str">
+        <v>["Mon","Tue","Wed","Thu","Fri","Sat","Sun"]</v>
+      </c>
+      <c r="F29" t="str">
+        <v>a6635d78-8321-470b-ba54-19fb00ecc897</v>
+      </c>
+      <c r="G29" t="str">
+        <v>a6635d78-8321-470b-ba54-19fb00ecc897</v>
+      </c>
+      <c r="H29" t="str">
+        <v>Seaplane</v>
+      </c>
+      <c r="I29" t="str">
+        <v>Age 2-11</v>
+      </c>
+      <c r="J29" t="str">
+        <v>Child</v>
+      </c>
+      <c r="K29">
+        <v>312</v>
+      </c>
+      <c r="L29">
+        <v>186</v>
+      </c>
+      <c r="M29" t="str">
+        <v>2025-01-01</v>
+      </c>
+      <c r="N29" t="str">
+        <v>2026-03-10</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>530a72f9-a1fb-488d-ab0d-479463e9010e</v>
+      </c>
+      <c r="B30" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C30" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D30" t="str">
+        <v>CTR-008-001</v>
+      </c>
+      <c r="E30" t="str">
+        <v>["Mon","Tue","Wed","Thu","Fri","Sat","Sun"]</v>
+      </c>
+      <c r="F30" t="str">
+        <v>c4302238-45ab-437a-8e35-756858676994</v>
+      </c>
+      <c r="G30" t="str">
+        <v>c4302238-45ab-437a-8e35-756858676994</v>
+      </c>
+      <c r="H30" t="str">
+        <v>Seaplane</v>
+      </c>
+      <c r="I30" t="str">
+        <v/>
+      </c>
+      <c r="J30" t="str">
+        <v>Adult</v>
+      </c>
+      <c r="K30">
+        <v>660</v>
+      </c>
+      <c r="L30">
+        <v>390</v>
+      </c>
+      <c r="M30" t="str">
+        <v>2025-10-01</v>
+      </c>
+      <c r="N30" t="str">
+        <v>2027-09-30</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>95dfc946-018f-47b5-9ab5-a2ef28acd1e0</v>
+      </c>
+      <c r="B31" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C31" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D31" t="str">
+        <v>CTR-008-001</v>
+      </c>
+      <c r="E31" t="str">
+        <v>["Mon","Tue","Wed","Thu","Fri","Sat","Sun"]</v>
+      </c>
+      <c r="F31" t="str">
+        <v>c4302238-45ab-437a-8e35-756858676994</v>
+      </c>
+      <c r="G31" t="str">
+        <v>c4302238-45ab-437a-8e35-756858676994</v>
+      </c>
+      <c r="H31" t="str">
+        <v>Seaplane</v>
+      </c>
+      <c r="I31" t="str">
+        <v>Age 2-11</v>
+      </c>
+      <c r="J31" t="str">
+        <v>Child</v>
+      </c>
+      <c r="K31">
+        <v>395</v>
+      </c>
+      <c r="L31">
+        <v>234</v>
+      </c>
+      <c r="M31" t="str">
+        <v>2025-10-01</v>
+      </c>
+      <c r="N31" t="str">
+        <v>2027-09-30</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>9a373d08-80e9-4a00-a556-b391225bee11</v>
+      </c>
+      <c r="B32" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C32" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D32" t="str">
+        <v>CTR-008-002</v>
+      </c>
+      <c r="E32" t="str">
+        <v>["Mon","Tue","Wed","Thu","Fri","Sat","Sun"]</v>
+      </c>
+      <c r="F32" t="str">
+        <v>c4302238-45ab-437a-8e35-756858676994</v>
+      </c>
+      <c r="G32" t="str">
+        <v>c4302238-45ab-437a-8e35-756858676994</v>
+      </c>
+      <c r="H32" t="str">
+        <v>Seaplane</v>
+      </c>
+      <c r="I32" t="str">
+        <v/>
+      </c>
+      <c r="J32" t="str">
+        <v>Adult</v>
+      </c>
+      <c r="K32">
+        <v>580</v>
+      </c>
+      <c r="L32">
+        <v>340</v>
+      </c>
+      <c r="M32" t="str">
+        <v>2025-10-01</v>
+      </c>
+      <c r="N32" t="str">
+        <v>2026-09-30</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>2e68c8ea-00c4-48f3-94a7-4e6b4693dbcf</v>
+      </c>
+      <c r="B33" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C33" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D33" t="str">
+        <v>CTR-008-002</v>
+      </c>
+      <c r="E33" t="str">
+        <v>["Mon","Tue","Wed","Thu","Fri","Sat","Sun"]</v>
+      </c>
+      <c r="F33" t="str">
+        <v>c4302238-45ab-437a-8e35-756858676994</v>
+      </c>
+      <c r="G33" t="str">
+        <v>c4302238-45ab-437a-8e35-756858676994</v>
+      </c>
+      <c r="H33" t="str">
+        <v>Seaplane</v>
+      </c>
+      <c r="I33" t="str">
+        <v>Age 2-11</v>
+      </c>
+      <c r="J33" t="str">
+        <v>Child</v>
+      </c>
+      <c r="K33">
+        <v>348</v>
+      </c>
+      <c r="L33">
+        <v>204</v>
+      </c>
+      <c r="M33" t="str">
+        <v>2025-10-01</v>
+      </c>
+      <c r="N33" t="str">
+        <v>2026-09-30</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>ab021eb8-bd6f-400e-a8ca-0edc5115b05b</v>
+      </c>
+      <c r="B34" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C34" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D34" t="str">
+        <v>CTR-009-001</v>
+      </c>
+      <c r="E34" t="str">
+        <v>["Mon","Tue","Wed","Thu","Fri","Sat","Sun"]</v>
+      </c>
+      <c r="F34" t="str">
+        <v>7a7a2625-26bd-424d-acbe-9c84fc54ea85</v>
+      </c>
+      <c r="G34" t="str">
+        <v>7a7a2625-26bd-424d-acbe-9c84fc54ea85</v>
+      </c>
+      <c r="H34" t="str">
+        <v>Speedboat</v>
+      </c>
+      <c r="I34" t="str">
+        <v/>
+      </c>
+      <c r="J34" t="str">
+        <v>Adult</v>
+      </c>
+      <c r="K34">
+        <v>350</v>
+      </c>
+      <c r="L34">
+        <v>210</v>
+      </c>
+      <c r="M34" t="str">
+        <v>2025-11-01</v>
+      </c>
+      <c r="N34" t="str">
+        <v>2026-10-31</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>edde193d-c8fa-470c-a2b0-72e3ad2bc425</v>
+      </c>
+      <c r="B35" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C35" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D35" t="str">
+        <v>CTR-009-001</v>
+      </c>
+      <c r="E35" t="str">
+        <v>["Mon","Tue","Wed","Thu","Fri","Sat","Sun"]</v>
+      </c>
+      <c r="F35" t="str">
+        <v>7a7a2625-26bd-424d-acbe-9c84fc54ea85</v>
+      </c>
+      <c r="G35" t="str">
+        <v>7a7a2625-26bd-424d-acbe-9c84fc54ea85</v>
+      </c>
+      <c r="H35" t="str">
+        <v>Speedboat</v>
+      </c>
+      <c r="I35" t="str">
+        <v>Age 2-11</v>
+      </c>
+      <c r="J35" t="str">
+        <v>Child</v>
+      </c>
+      <c r="K35">
+        <v>210</v>
+      </c>
+      <c r="L35">
+        <v>125</v>
+      </c>
+      <c r="M35" t="str">
+        <v>2025-11-01</v>
+      </c>
+      <c r="N35" t="str">
+        <v>2026-10-31</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>b70083ef-9379-47c0-b3e9-936131584fb4</v>
+      </c>
+      <c r="B36" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C36" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D36" t="str">
+        <v>CTR-010-001</v>
+      </c>
+      <c r="E36" t="str">
+        <v>["Mon","Tue","Wed","Thu","Fri","Sat","Sun"]</v>
+      </c>
+      <c r="F36" t="str">
+        <v>a6317543-34f5-4949-96ef-e195ab1aa389</v>
+      </c>
+      <c r="G36" t="str">
+        <v>a6317543-34f5-4949-96ef-e195ab1aa389</v>
+      </c>
+      <c r="H36" t="str">
+        <v>Seaplane</v>
+      </c>
+      <c r="I36" t="str">
+        <v/>
+      </c>
+      <c r="J36" t="str">
+        <v>Adult</v>
+      </c>
+      <c r="K36">
+        <v>710</v>
+      </c>
+      <c r="L36">
+        <v>420</v>
+      </c>
+      <c r="M36" t="str">
+        <v>2024-03-01</v>
+      </c>
+      <c r="N36" t="str">
+        <v>2025-02-28</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>f6ef7488-3648-499c-9a6a-152532c8deeb</v>
+      </c>
+      <c r="B37" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C37" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D37" t="str">
+        <v>CTR-010-001</v>
+      </c>
+      <c r="E37" t="str">
+        <v>["Mon","Tue","Wed","Thu","Fri","Sat","Sun"]</v>
+      </c>
+      <c r="F37" t="str">
+        <v>a6317543-34f5-4949-96ef-e195ab1aa389</v>
+      </c>
+      <c r="G37" t="str">
+        <v>a6317543-34f5-4949-96ef-e195ab1aa389</v>
+      </c>
+      <c r="H37" t="str">
+        <v>Seaplane</v>
+      </c>
+      <c r="I37" t="str">
+        <v>Age 2-11</v>
+      </c>
+      <c r="J37" t="str">
+        <v>Child</v>
+      </c>
+      <c r="K37">
         <v>425</v>
       </c>
-      <c r="L21">
+      <c r="L37">
         <v>252</v>
       </c>
-      <c r="M21" t="str">
+      <c r="M37" t="str">
         <v>2024-03-01</v>
       </c>
-      <c r="N21" t="str">
+      <c r="N37" t="str">
+        <v>2025-02-28</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>8e38815b-bd86-43fb-814f-55d6df7f699f</v>
+      </c>
+      <c r="B38" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C38" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D38" t="str">
+        <v>CTR-010-002</v>
+      </c>
+      <c r="E38" t="str">
+        <v>["Mon","Tue","Wed","Thu","Fri","Sat","Sun"]</v>
+      </c>
+      <c r="F38" t="str">
+        <v>a6317543-34f5-4949-96ef-e195ab1aa389</v>
+      </c>
+      <c r="G38" t="str">
+        <v>a6317543-34f5-4949-96ef-e195ab1aa389</v>
+      </c>
+      <c r="H38" t="str">
+        <v>Seaplane</v>
+      </c>
+      <c r="I38" t="str">
+        <v/>
+      </c>
+      <c r="J38" t="str">
+        <v>Adult</v>
+      </c>
+      <c r="K38">
+        <v>550</v>
+      </c>
+      <c r="L38">
+        <v>325</v>
+      </c>
+      <c r="M38" t="str">
+        <v>2024-03-01</v>
+      </c>
+      <c r="N38" t="str">
+        <v>2025-02-28</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>fb7d9445-dcb2-409e-9d05-42f071294ad5</v>
+      </c>
+      <c r="B39" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C39" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D39" t="str">
+        <v>CTR-010-002</v>
+      </c>
+      <c r="E39" t="str">
+        <v>["Mon","Tue","Wed","Thu","Fri","Sat","Sun"]</v>
+      </c>
+      <c r="F39" t="str">
+        <v>a6317543-34f5-4949-96ef-e195ab1aa389</v>
+      </c>
+      <c r="G39" t="str">
+        <v>a6317543-34f5-4949-96ef-e195ab1aa389</v>
+      </c>
+      <c r="H39" t="str">
+        <v>Seaplane</v>
+      </c>
+      <c r="I39" t="str">
+        <v>Age 2-11</v>
+      </c>
+      <c r="J39" t="str">
+        <v>Child</v>
+      </c>
+      <c r="K39">
+        <v>330</v>
+      </c>
+      <c r="L39">
+        <v>195</v>
+      </c>
+      <c r="M39" t="str">
+        <v>2024-03-01</v>
+      </c>
+      <c r="N39" t="str">
         <v>2025-02-28</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N39"/>
   </ignoredErrors>
 </worksheet>
 </file>